--- a/output/pdf_financials_xlsx/GAMA.xlsx
+++ b/output/pdf_financials_xlsx/GAMA.xlsx
@@ -5731,22 +5731,22 @@
         <v>2.959809</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>3.130902</v>
+        <v>4.245042</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.683301</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.707556</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.803809</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.803809</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.442667</v>
       </c>
     </row>
     <row r="93">
@@ -9408,7 +9408,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10648,7 +10652,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11324,7 +11332,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GAMA.xlsx
+++ b/output/pdf_financials_xlsx/GAMA.xlsx
@@ -2399,52 +2399,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.230669</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.326532</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09747500000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.029575</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.041727</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.008185</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001777</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.046108</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.122805</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.26901</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.138104</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.081232</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.828194</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.183456</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.002003</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.240392</v>
       </c>
     </row>
     <row r="35">
@@ -2509,52 +2509,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.230669</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.25</v>
+        <v>3.576532</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.85</v>
+        <v>1.947475</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.429575</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.041727</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.008185</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001777</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.046108</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.122805</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.26901</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.138104</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.081232</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.828194</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.183456</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.002003</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.240392</v>
       </c>
     </row>
     <row r="37">
@@ -3169,28 +3169,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.26146</v>
+        <v>0.030791</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.399897</v>
+        <v>0.073365</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.185509</v>
+        <v>0.088034</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.055525</v>
+        <v>0.02595</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.051769</v>
+        <v>0.010042</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.033602</v>
+        <v>0.025417</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.026277</v>
+        <v>0.0245</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.066108</v>
+        <v>0.02</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.159312</v>
+        <v>0.021208</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.13277</v>
+        <v>0.051538</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.85569</v>
+        <v>0.027496</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.241868</v>
+        <v>0.058412</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.243935</v>
+        <v>0.241932</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.44854</v>
+        <v>0.208148</v>
       </c>
     </row>
     <row r="49">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
